--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA9A6F5-1E5A-46A2-8D95-62E565673956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B29BCF0-0F2A-48B3-B70B-BB4675455CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B29BCF0-0F2A-48B3-B70B-BB4675455CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DE898E-15FA-4889-89D7-11DA2476C6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DE898E-15FA-4889-89D7-11DA2476C6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4DFBDB-0C34-4B7A-8E8B-32CF42F07725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4DFBDB-0C34-4B7A-8E8B-32CF42F07725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BB5439-D635-4BE9-B388-E2B1306151F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BB5439-D635-4BE9-B388-E2B1306151F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A202068-8C4C-4BA1-A7F6-93F0C633CE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A202068-8C4C-4BA1-A7F6-93F0C633CE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E1422A-EC6A-41A1-B57B-60805DC00ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E1422A-EC6A-41A1-B57B-60805DC00ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A9DDC8-8FB9-417A-B259-C541C9A03C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A9DDC8-8FB9-417A-B259-C541C9A03C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C2610A-3DD8-44AD-BD6E-B975893F5D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C2610A-3DD8-44AD-BD6E-B975893F5D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F580F5E6-738D-4842-9AD3-CD389426C29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="133">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -166,6 +166,9 @@
     <t>Nabil</t>
   </si>
   <si>
+    <t>31/12/1899</t>
+  </si>
+  <si>
     <t>16/09/2025</t>
   </si>
   <si>
@@ -199,7 +202,7 @@
     <t>Patricia</t>
   </si>
   <si>
-    <t>RDC</t>
+    <t>République démocratique du Congo</t>
   </si>
   <si>
     <t>26/11/2025</t>
@@ -902,7 +905,7 @@
     <col min="2" max="2" width="13" style="5" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" style="5" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="9" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" customWidth="1"/>
@@ -1149,7 +1152,7 @@
         <v>46</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>24</v>
@@ -1158,7 +1161,7 @@
         <v>25</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
@@ -1169,13 +1172,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>43</v>
@@ -1195,22 +1198,22 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>15</v>
@@ -1221,22 +1224,22 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>15</v>
@@ -1247,22 +1250,22 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>15</v>
@@ -1273,22 +1276,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
@@ -1299,22 +1302,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
@@ -1325,13 +1328,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>43</v>
@@ -1340,7 +1343,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
@@ -1351,22 +1354,22 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -1377,13 +1380,13 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>43</v>
@@ -1392,7 +1395,7 @@
         <v>13</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
@@ -1403,22 +1406,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
@@ -1429,22 +1432,22 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -1455,22 +1458,22 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -1481,22 +1484,22 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -1507,16 +1510,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>13</v>
@@ -1533,13 +1536,13 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>43</v>
@@ -1548,7 +1551,7 @@
         <v>13</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -1559,22 +1562,22 @@
         <v>24</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -1585,22 +1588,22 @@
         <v>25</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -1611,13 +1614,13 @@
         <v>26</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -1626,7 +1629,7 @@
         <v>13</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -1637,22 +1640,22 @@
         <v>27</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -1663,22 +1666,22 @@
         <v>28</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F580F5E6-738D-4842-9AD3-CD389426C29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617BB896-6AE5-4CF5-8491-874D16E83F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="132">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -164,9 +164,6 @@
   </si>
   <si>
     <t>Nabil</t>
-  </si>
-  <si>
-    <t>31/12/1899</t>
   </si>
   <si>
     <t>16/09/2025</t>
@@ -1152,7 +1149,7 @@
         <v>46</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>24</v>
@@ -1161,7 +1158,7 @@
         <v>25</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
@@ -1172,13 +1169,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>43</v>
@@ -1198,22 +1195,22 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>15</v>
@@ -1224,22 +1221,22 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>59</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>60</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>15</v>
@@ -1250,22 +1247,22 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="E15" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>15</v>
@@ -1276,22 +1273,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
@@ -1302,22 +1299,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="F17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
@@ -1328,13 +1325,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>43</v>
@@ -1343,7 +1340,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
@@ -1354,22 +1351,22 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="E19" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -1380,13 +1377,13 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="D20" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>43</v>
@@ -1395,7 +1392,7 @@
         <v>13</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
@@ -1406,22 +1403,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="D21" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="E21" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
@@ -1432,22 +1429,22 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="E22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -1458,22 +1455,22 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="D23" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="E23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -1484,22 +1481,22 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="D24" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>102</v>
-      </c>
       <c r="E24" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -1510,16 +1507,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>13</v>
@@ -1536,13 +1533,13 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="D26" s="10" t="s">
         <v>107</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>108</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>43</v>
@@ -1551,7 +1548,7 @@
         <v>13</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -1562,22 +1559,22 @@
         <v>24</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="D27" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="E27" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -1588,22 +1585,22 @@
         <v>25</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="D28" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="E28" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -1614,13 +1611,13 @@
         <v>26</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="D29" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -1629,7 +1626,7 @@
         <v>13</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -1640,22 +1637,22 @@
         <v>27</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="D30" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="E30" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -1666,22 +1663,22 @@
         <v>28</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="D31" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="E31" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617BB896-6AE5-4CF5-8491-874D16E83F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC2D935-D404-4643-80B7-850304819E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="84">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Mariami</t>
   </si>
   <si>
-    <t>23/08/1991</t>
+    <t/>
   </si>
   <si>
     <t>Géorgie</t>
@@ -67,132 +67,78 @@
     <t>F</t>
   </si>
   <si>
-    <t>20/11/2025</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>ABDOU</t>
   </si>
   <si>
     <t>Houfranie</t>
   </si>
   <si>
-    <t>31/12/1978</t>
-  </si>
-  <si>
     <t>Comores</t>
   </si>
   <si>
-    <t>01/09/2025</t>
-  </si>
-  <si>
     <t>AHED MOHAMED</t>
   </si>
   <si>
     <t>Mohamed</t>
   </si>
   <si>
-    <t>22/07/1993</t>
-  </si>
-  <si>
     <t>Soudan</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>01/05/2024</t>
-  </si>
-  <si>
     <t>ALHAJ</t>
   </si>
   <si>
     <t>Mudother</t>
   </si>
   <si>
-    <t>08/04/1999</t>
-  </si>
-  <si>
-    <t>25/11/2024</t>
-  </si>
-  <si>
     <t>BEGUM</t>
   </si>
   <si>
     <t>Lima</t>
   </si>
   <si>
-    <t>10/12/1990</t>
-  </si>
-  <si>
     <t>Bangladesh</t>
   </si>
   <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
     <t>CHKHAPELIA</t>
   </si>
   <si>
     <t>Tamta</t>
   </si>
   <si>
-    <t>01/04/1992</t>
-  </si>
-  <si>
-    <t>01/01/2022</t>
-  </si>
-  <si>
     <t>DIAMPITISA</t>
   </si>
   <si>
     <t>Madalena</t>
   </si>
   <si>
-    <t>02/11/1967</t>
-  </si>
-  <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
     <t>EBRAHIM DUD</t>
   </si>
   <si>
     <t>Nabil</t>
   </si>
   <si>
-    <t>16/09/2025</t>
-  </si>
-  <si>
     <t>EDUARDO</t>
   </si>
   <si>
     <t>Kiala Baptista</t>
   </si>
   <si>
-    <t>31/12/1994</t>
-  </si>
-  <si>
     <t>ELIDRISSI BOUANANI</t>
   </si>
   <si>
     <t>Fatima</t>
   </si>
   <si>
-    <t>01/01/1959</t>
-  </si>
-  <si>
     <t>Maroc</t>
   </si>
   <si>
-    <t>15/09/2022</t>
-  </si>
-  <si>
     <t>FURAH KITAMBALA</t>
   </si>
   <si>
@@ -202,48 +148,30 @@
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>26/11/2025</t>
-  </si>
-  <si>
     <t>HASHEMI</t>
   </si>
   <si>
     <t>Asghar</t>
   </si>
   <si>
-    <t>28/02/1999</t>
-  </si>
-  <si>
     <t>Afghanistan</t>
   </si>
   <si>
-    <t>09/10/2025</t>
-  </si>
-  <si>
     <t>IMERI</t>
   </si>
   <si>
     <t>Mirela</t>
   </si>
   <si>
-    <t>30/05/1977</t>
-  </si>
-  <si>
     <t>Albanie</t>
   </si>
   <si>
-    <t>10/05/2022</t>
-  </si>
-  <si>
     <t>IREDIA</t>
   </si>
   <si>
     <t>Tracy</t>
   </si>
   <si>
-    <t>27/07/1982</t>
-  </si>
-  <si>
     <t>Nigéria</t>
   </si>
   <si>
@@ -253,114 +181,66 @@
     <t>Febe</t>
   </si>
   <si>
-    <t>05/03/2001</t>
-  </si>
-  <si>
     <t>JARA</t>
   </si>
   <si>
     <t>Mario</t>
   </si>
   <si>
-    <t>19/01/2003</t>
-  </si>
-  <si>
     <t>Chili</t>
   </si>
   <si>
-    <t>18/09/2025</t>
-  </si>
-  <si>
     <t>KINAVUIDI</t>
   </si>
   <si>
     <t>Viviane</t>
   </si>
   <si>
-    <t>29/06/1988</t>
-  </si>
-  <si>
-    <t>10/09/2025</t>
-  </si>
-  <si>
     <t>LAGOUNE</t>
   </si>
   <si>
     <t>Ilham</t>
   </si>
   <si>
-    <t>15/08/2002</t>
-  </si>
-  <si>
     <t>Algérie</t>
   </si>
   <si>
-    <t>07/11/2025</t>
-  </si>
-  <si>
     <t>LUMBE OMOWO</t>
   </si>
   <si>
     <t>Anne-Marie</t>
   </si>
   <si>
-    <t>18/03/1979</t>
-  </si>
-  <si>
-    <t>25/11/2025</t>
-  </si>
-  <si>
     <t>MADALENA</t>
   </si>
   <si>
     <t>Lidia</t>
   </si>
   <si>
-    <t>29/05/2018</t>
-  </si>
-  <si>
-    <t>14/11/2025</t>
-  </si>
-  <si>
     <t>MATETA</t>
   </si>
   <si>
     <t>Gloria</t>
   </si>
   <si>
-    <t>30/07/1994</t>
-  </si>
-  <si>
     <t>NGELI</t>
   </si>
   <si>
     <t>Yolande</t>
   </si>
   <si>
-    <t>06/12/1980</t>
-  </si>
-  <si>
     <t xml:space="preserve">OLIVEIRA </t>
   </si>
   <si>
     <t>Laura</t>
   </si>
   <si>
-    <t>14/12/1986</t>
-  </si>
-  <si>
-    <t>02/06/2024</t>
-  </si>
-  <si>
     <t>RIAHI</t>
   </si>
   <si>
     <t>Souhail</t>
   </si>
   <si>
-    <t>13/11/1992</t>
-  </si>
-  <si>
     <t>Tunisie</t>
   </si>
   <si>
@@ -370,55 +250,31 @@
     <t>Nawa</t>
   </si>
   <si>
-    <t>15/11/1996</t>
-  </si>
-  <si>
     <t>Côte d'Ivoire</t>
   </si>
   <si>
-    <t>01/10/2024</t>
-  </si>
-  <si>
     <t>TINIKASCHVILI</t>
   </si>
   <si>
     <t>Maka</t>
   </si>
   <si>
-    <t>21/09/1983</t>
-  </si>
-  <si>
-    <t>12/10/2021</t>
-  </si>
-  <si>
     <t>TONOYAN</t>
   </si>
   <si>
     <t>Alvard</t>
   </si>
   <si>
-    <t>10/01/1963</t>
-  </si>
-  <si>
     <t>Ukraine</t>
   </si>
   <si>
-    <t>12/01/2016</t>
-  </si>
-  <si>
     <t>VIUCHE GIRON</t>
   </si>
   <si>
     <t>Sanyi</t>
   </si>
   <si>
-    <t>21/05/1995</t>
-  </si>
-  <si>
     <t>Colombie</t>
-  </si>
-  <si>
-    <t>06/03/2025</t>
   </si>
 </sst>
 </file>
@@ -976,10 +832,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -987,25 +843,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="F5" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1013,25 +869,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1039,25 +895,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1065,25 +921,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1091,13 +947,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>12</v>
@@ -1106,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1117,25 +973,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1143,25 +999,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1169,25 +1025,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1195,25 +1051,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1221,25 +1077,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1247,25 +1103,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1273,25 +1129,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1299,25 +1155,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1325,25 +1181,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1351,25 +1207,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1377,25 +1233,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1403,25 +1259,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1429,25 +1285,25 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1455,25 +1311,25 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1481,25 +1337,25 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1507,25 +1363,25 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1533,25 +1389,25 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>108</v>
+        <v>11</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1559,25 +1415,25 @@
         <v>24</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1585,25 +1441,25 @@
         <v>25</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>115</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1611,13 +1467,13 @@
         <v>26</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -1626,10 +1482,10 @@
         <v>13</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1637,25 +1493,25 @@
         <v>27</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1663,25 +1519,25 @@
         <v>28</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="39.950000000000003" customHeight="1">

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC2D935-D404-4643-80B7-850304819E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C52045-B5ED-4E12-89A6-1638B8D671F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C52045-B5ED-4E12-89A6-1638B8D671F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1CF0ED-667F-470E-BEFD-20E24ED9426F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="132">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Mariami</t>
   </si>
   <si>
-    <t/>
+    <t>23/08/1991</t>
   </si>
   <si>
     <t>Géorgie</t>
@@ -67,78 +67,132 @@
     <t>F</t>
   </si>
   <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
     <t>ABDOU</t>
   </si>
   <si>
     <t>Houfranie</t>
   </si>
   <si>
+    <t>31/12/1978</t>
+  </si>
+  <si>
     <t>Comores</t>
   </si>
   <si>
+    <t>01/09/2025</t>
+  </si>
+  <si>
     <t>AHED MOHAMED</t>
   </si>
   <si>
     <t>Mohamed</t>
   </si>
   <si>
+    <t>22/07/1993</t>
+  </si>
+  <si>
     <t>Soudan</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
+    <t>01/05/2024</t>
+  </si>
+  <si>
     <t>ALHAJ</t>
   </si>
   <si>
     <t>Mudother</t>
   </si>
   <si>
+    <t>08/04/1999</t>
+  </si>
+  <si>
+    <t>25/11/2024</t>
+  </si>
+  <si>
     <t>BEGUM</t>
   </si>
   <si>
     <t>Lima</t>
   </si>
   <si>
+    <t>10/12/1990</t>
+  </si>
+  <si>
     <t>Bangladesh</t>
   </si>
   <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
     <t>CHKHAPELIA</t>
   </si>
   <si>
     <t>Tamta</t>
   </si>
   <si>
+    <t>01/04/1992</t>
+  </si>
+  <si>
+    <t>01/01/2022</t>
+  </si>
+  <si>
     <t>DIAMPITISA</t>
   </si>
   <si>
     <t>Madalena</t>
   </si>
   <si>
+    <t>02/11/1967</t>
+  </si>
+  <si>
     <t>Angola</t>
   </si>
   <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
     <t>EBRAHIM DUD</t>
   </si>
   <si>
     <t>Nabil</t>
   </si>
   <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
     <t>EDUARDO</t>
   </si>
   <si>
     <t>Kiala Baptista</t>
   </si>
   <si>
+    <t>31/12/1994</t>
+  </si>
+  <si>
     <t>ELIDRISSI BOUANANI</t>
   </si>
   <si>
     <t>Fatima</t>
   </si>
   <si>
+    <t>01/01/1959</t>
+  </si>
+  <si>
     <t>Maroc</t>
   </si>
   <si>
+    <t>15/09/2022</t>
+  </si>
+  <si>
     <t>FURAH KITAMBALA</t>
   </si>
   <si>
@@ -148,30 +202,48 @@
     <t>République démocratique du Congo</t>
   </si>
   <si>
+    <t>26/11/2025</t>
+  </si>
+  <si>
     <t>HASHEMI</t>
   </si>
   <si>
     <t>Asghar</t>
   </si>
   <si>
+    <t>28/02/1999</t>
+  </si>
+  <si>
     <t>Afghanistan</t>
   </si>
   <si>
+    <t>09/10/2025</t>
+  </si>
+  <si>
     <t>IMERI</t>
   </si>
   <si>
     <t>Mirela</t>
   </si>
   <si>
+    <t>30/05/1977</t>
+  </si>
+  <si>
     <t>Albanie</t>
   </si>
   <si>
+    <t>10/05/2022</t>
+  </si>
+  <si>
     <t>IREDIA</t>
   </si>
   <si>
     <t>Tracy</t>
   </si>
   <si>
+    <t>27/07/1982</t>
+  </si>
+  <si>
     <t>Nigéria</t>
   </si>
   <si>
@@ -181,66 +253,114 @@
     <t>Febe</t>
   </si>
   <si>
+    <t>05/03/2001</t>
+  </si>
+  <si>
     <t>JARA</t>
   </si>
   <si>
     <t>Mario</t>
   </si>
   <si>
+    <t>19/01/2003</t>
+  </si>
+  <si>
     <t>Chili</t>
   </si>
   <si>
+    <t>18/09/2025</t>
+  </si>
+  <si>
     <t>KINAVUIDI</t>
   </si>
   <si>
     <t>Viviane</t>
   </si>
   <si>
+    <t>29/06/1988</t>
+  </si>
+  <si>
+    <t>10/09/2025</t>
+  </si>
+  <si>
     <t>LAGOUNE</t>
   </si>
   <si>
     <t>Ilham</t>
   </si>
   <si>
+    <t>15/08/2002</t>
+  </si>
+  <si>
     <t>Algérie</t>
   </si>
   <si>
+    <t>07/11/2025</t>
+  </si>
+  <si>
     <t>LUMBE OMOWO</t>
   </si>
   <si>
     <t>Anne-Marie</t>
   </si>
   <si>
+    <t>18/03/1979</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
     <t>MADALENA</t>
   </si>
   <si>
     <t>Lidia</t>
   </si>
   <si>
+    <t>29/05/2018</t>
+  </si>
+  <si>
+    <t>14/11/2025</t>
+  </si>
+  <si>
     <t>MATETA</t>
   </si>
   <si>
     <t>Gloria</t>
   </si>
   <si>
+    <t>30/07/1994</t>
+  </si>
+  <si>
     <t>NGELI</t>
   </si>
   <si>
     <t>Yolande</t>
   </si>
   <si>
+    <t>06/12/1980</t>
+  </si>
+  <si>
     <t xml:space="preserve">OLIVEIRA </t>
   </si>
   <si>
     <t>Laura</t>
   </si>
   <si>
+    <t>14/12/1986</t>
+  </si>
+  <si>
+    <t>02/06/2024</t>
+  </si>
+  <si>
     <t>RIAHI</t>
   </si>
   <si>
     <t>Souhail</t>
   </si>
   <si>
+    <t>13/11/1992</t>
+  </si>
+  <si>
     <t>Tunisie</t>
   </si>
   <si>
@@ -250,31 +370,55 @@
     <t>Nawa</t>
   </si>
   <si>
+    <t>15/11/1996</t>
+  </si>
+  <si>
     <t>Côte d'Ivoire</t>
   </si>
   <si>
+    <t>01/10/2024</t>
+  </si>
+  <si>
     <t>TINIKASCHVILI</t>
   </si>
   <si>
     <t>Maka</t>
   </si>
   <si>
+    <t>21/09/1983</t>
+  </si>
+  <si>
+    <t>12/10/2021</t>
+  </si>
+  <si>
     <t>TONOYAN</t>
   </si>
   <si>
     <t>Alvard</t>
   </si>
   <si>
+    <t>10/01/1963</t>
+  </si>
+  <si>
     <t>Ukraine</t>
   </si>
   <si>
+    <t>12/01/2016</t>
+  </si>
+  <si>
     <t>VIUCHE GIRON</t>
   </si>
   <si>
     <t>Sanyi</t>
   </si>
   <si>
+    <t>21/05/1995</t>
+  </si>
+  <si>
     <t>Colombie</t>
+  </si>
+  <si>
+    <t>06/03/2025</t>
   </si>
 </sst>
 </file>
@@ -832,10 +976,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -843,25 +987,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -869,25 +1013,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -895,25 +1039,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -921,25 +1065,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -947,13 +1091,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>12</v>
@@ -962,10 +1106,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -973,25 +1117,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -999,25 +1143,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1025,25 +1169,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>11</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1051,25 +1195,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1077,25 +1221,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1103,25 +1247,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1129,25 +1273,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1155,25 +1299,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>11</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1181,25 +1325,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1207,25 +1351,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1233,25 +1377,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1259,25 +1403,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1285,25 +1429,25 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1311,25 +1455,25 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1337,25 +1481,25 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1363,25 +1507,25 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1389,25 +1533,25 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1415,25 +1559,25 @@
         <v>24</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1441,25 +1585,25 @@
         <v>25</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1467,13 +1611,13 @@
         <v>26</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -1482,10 +1626,10 @@
         <v>13</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1493,25 +1637,25 @@
         <v>27</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>11</v>
+        <v>124</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1519,25 +1663,25 @@
         <v>28</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>11</v>
+        <v>131</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="39.950000000000003" customHeight="1">
